--- a/xlsx/packagedataCN20260413 special cargo-HQ.xlsx
+++ b/xlsx/packagedataCN20260413 special cargo-HQ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382A03CC-E76E-41CA-BC81-AA956AE15165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4E9151-BCD4-40E1-8C27-078E4C5BA88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="17">
   <si>
     <t>否</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,10 @@
   </si>
   <si>
     <t>是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包箱数量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.08203125" bestFit="1" customWidth="1"/>
@@ -436,9 +440,10 @@
     <col min="5" max="5" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -467,13 +472,16 @@
         <v>11</v>
       </c>
       <c r="J1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -501,14 +509,17 @@
       <c r="I2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
@@ -536,14 +547,17 @@
       <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -571,14 +585,17 @@
       <c r="I4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -606,10 +623,13 @@
       <c r="I5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>0</v>
       </c>
     </row>
